--- a/mi-app/razas.xlsx
+++ b/mi-app/razas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\traselcaos\mi-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{633F23EC-246C-4F17-8217-F0D465C86AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A96D22-2FA2-4ED4-A569-983F6EFD5E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>especie</t>
   </si>
@@ -68,7 +68,94 @@
     <t>Ya consolidados dentro de la Asociación Cealtar Universal, los Nastajiri se ven envueltos en un acontecimiento que los llevará a reencontrarse con el legado de Arsuen.</t>
   </si>
   <si>
-    <t>Fatith</t>
+    <t>Abandonada y privada de parte de su memoria, esta especie dedicó sus esfuerzos a preservar su material genético mediante la experimentación con formas de vida cercanas. Aunque ignora sus orígenes y las razones de su exilio en un mundo frío e inhóspito, conserva amplios conocimientos científicos y fragmentos de memoria sobre otras especies y las leyes que regulan la paz entre civilizaciones.</t>
+  </si>
+  <si>
+    <t>Xaofeir</t>
+  </si>
+  <si>
+    <t>La desesperación por preservar su linaje genético, sumada al desconocimiento de sus propios orígenes, ha sembrado un clima de desconfianza y traición entre los Fatith. En medio de ese caos, dieron origen sin saberlo a un ser de inmenso poder cuya única razón de existir es la venganza.</t>
+  </si>
+  <si>
+    <t>Es una especie avanzada que forma parte de la Asociación Cealtar Universal, una organización dedicada a la protección y supervisión de especies primitivas e intermedias. Son reconocidos por haber establecido contacto discreto con los Nastajiri con el fin de guiarlos hacia un propósito de mayor relevancia para el futuro del universo.</t>
+  </si>
+  <si>
+    <t>Nafim expone, a través de sus enseñanzas, que la convivencia entre especies requiere tanto de un orden estructurado como de la presencia inevitable del caos.</t>
+  </si>
+  <si>
+    <t>Tras un encuentro inesperado de varias especies, Dehuga reúne a distintas especies de la Asociación Cealtar Universal con el propósito de recordar el pasado y tomar una decisión determinante, mientras guarda un as bajo la manga.</t>
+  </si>
+  <si>
+    <t>Vel-Verlander</t>
+  </si>
+  <si>
+    <t>Abandonados junto a los Fatith, esta especie ha perdido casi todo recuerdo de su pasado y sus orígenes, sin mostrar interés en recuperarlos. Han sido utilizados como herramientas por los Fatith para llevar a cabo tareas que estos no pueden realizar directamente.</t>
+  </si>
+  <si>
+    <t>Vel-Fatith</t>
+  </si>
+  <si>
+    <t>Su función consiste en realizar experimentos con diversas especies, así como mediciones ambientales en distintos planetas, en nombre de los Fatith.</t>
+  </si>
+  <si>
+    <t>Ratti Pem'ya</t>
+  </si>
+  <si>
+    <t>El progreso de esta especie se atribuye a la guía y consejo de una deidad de pasado enigmático. Han permanecido al margen de las alianzas y conflictos interestelares, pero la llegada de la Noc-Auli a su planeta marcará un punto de inflexión en su historia.</t>
+  </si>
+  <si>
+    <t>Noc-Auli</t>
+  </si>
+  <si>
+    <t>Especie clónica al servicio de los Hostiles, empleada para ejecutar tareas en distintos planetas.</t>
+  </si>
+  <si>
+    <t>“La Mezcla” constituye una facción parcialmente consciente de la Noc-Auli que ha llegado al planeta de los Ratti en busca de investigación y comprensión de aquello que el resto de su especie no puede alcanzar. Sus breves momentos de conciencia les otorgan emociones que no logran comprender, pero que podrían resultar clave para forjar una alianza duradera.</t>
+  </si>
+  <si>
+    <t>Una vez más, el uso de individuos de esta especie podría acarrear repercusiones imprevistas para los propios Hostiles al mando.</t>
+  </si>
+  <si>
+    <t>Tras una serie de eventos desastrosos en su planeta, aislado del contacto externo, los Ratti se ven envueltos en una situación que pondrá en riesgo el orden y la paz que han intentado preservar.</t>
+  </si>
+  <si>
+    <t>Su papel no consiste únicamente en servir de vínculo entre especies muy distintas, sino también en influir indirectamente en la voluntad de un individuo hacia fines que le resultarían impensables.</t>
+  </si>
+  <si>
+    <t>Taílyas</t>
+  </si>
+  <si>
+    <t>Mugtatarios</t>
+  </si>
+  <si>
+    <t>Especie que explora la transición entre una civilización intermedia y una avanzada, y que termina descubriendo que su papel es más importante de lo que había imaginado.</t>
+  </si>
+  <si>
+    <t>Tras su llegada al planeta Mugta, se adentrarán en los complejos conceptos que rigen la realidad. Encoa deberá tomar una decisión que definirá el lugar de su especie en el universo.</t>
+  </si>
+  <si>
+    <t>A medida que los Taílyas se adentran en el conflicto entre especies, comienzan a preguntarse si realmente están del lado correcto, lo que los impulsa a cuestionar su papel y a buscar su verdadero lugar entre ellas.</t>
+  </si>
+  <si>
+    <t>Especie avanzada integrante de la Orden Cósmica del Espacio. Junto a otras cuatro razas, constituye uno de los principales actores interesados en la unión del Destello del Espacio y el del Tiempo con el objetivo de poner fin al caos universal.</t>
+  </si>
+  <si>
+    <t>Al recibir la visita de los Taílyas, les revelarán los conflictos que se ciernen entre las especies consideradas favorables al progreso. Por su parte, Nálika permite a Encoa decidir si desea unirse a la misión de los Aliados o no.</t>
+  </si>
+  <si>
+    <t>Con el fin de alcanzar su objetivo final, intentan proteger el cuerpo de Nálika mientras adaptan sus defensas a las circunstancias externas que afectan a sus aliados, aunque la situación terminará escapándoseles de las manos.</t>
+  </si>
+  <si>
+    <t>Gúas</t>
+  </si>
+  <si>
+    <t>Assul</t>
+  </si>
+  <si>
+    <t>Fegiste</t>
+  </si>
+  <si>
+    <t>Nandia</t>
   </si>
 </sst>
 </file>
@@ -104,9 +191,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -443,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2E1CDB-3816-4A77-8E43-47460061F5E7}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="38.109375" style="1" customWidth="1"/>
@@ -483,9 +573,116 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/mi-app/razas.xlsx
+++ b/mi-app/razas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\traselcaos\mi-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A96D22-2FA2-4ED4-A569-983F6EFD5E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE67222-6C2E-4C7F-838F-044283101EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>especie</t>
   </si>
@@ -156,6 +156,39 @@
   </si>
   <si>
     <t>Nandia</t>
+  </si>
+  <si>
+    <t>Especie reconocida durante la última era bélica, cuando Ignua asumió el control del reino con el propósito de someter a una especie hostil. Los conflictos fueron breves, pues los Gúas demostraron ser implacables y poseer una notable superioridad estratégica.</t>
+  </si>
+  <si>
+    <t>Se distinguen como una especie guerrera, especialmente valiosa en tiempos de conflicto, durante los cuales su liderazgo suele cambiar de forma temporal para adaptarse a las exigencias de la guerra.</t>
+  </si>
+  <si>
+    <t>Tras la desaparición de Olen y el retroceso de Nandia, los Gúas asumen el control de la defensa planetaria con el objetivo de salvaguardar la misión de la Orden Cósmica. Sin embargo, sus decisiones orientadas a la guerra desencadenarán una serie de acontecimientos que agravarán aún más la situación a escala global.</t>
+  </si>
+  <si>
+    <t>Esta especie surgió hace mucho tiempo como resultado de la modificación genética de razas hostiles. De aquella mezcla nacieron individuos cuyas decisiones y formas de comunicación dependen más de sus sentidos que de la razón. Lejos de ser una desventaja, esta cualidad les resulta eficaz, ya que sus cuerpos están adaptados para emitir distintos aromas según su estado emocional y condición física.  Junto a los Mugtatarios, fundaron la Orden Cósmica con el propósito de proteger el destello de Nálika. Desde entonces, se comprometieron a acoger en sus filas a cualquier raza dispuesta a entregarlo todo por esa causa, incluso si carecía de una gran fuerza militar.</t>
+  </si>
+  <si>
+    <t>Los Assul se presentan como una especie que, pese a ser fundadora de la Orden Cósmica del Espacio junto a los Mugtatarios, mantiene alianzas externas a dicha organización con el fin de adaptarse y sobrevivir en un universo marcado por intereses diversos.</t>
+  </si>
+  <si>
+    <t>Se erigen como los principales castigadores de los Nandia tras su reclusión en su planeta. Los Assul aprovechan esta situación para inclinar sus alianzas externas a su favor y fortalecer su posición.</t>
+  </si>
+  <si>
+    <t>Los Fegiste, concebidos originalmente como una especie al servicio de razas hostiles, fueron abandonados tras un experimento fallido que les otorgó conciencia de su propia existencia. A partir de entonces, evolucionaron de manera independiente, desarrollando un profundo interés por comprender los sentimientos de otras especies, ya que ellos eran incapaces de experimentarlos en su totalidad. Esta curiosidad los llevó a entrar en contacto con los Mugtatarios, a quienes inicialmente estudiaron y con quienes, más adelante, formaron una alianza. Su decisión de apoyar a la Orden Cósmica surgió tanto de este vínculo como de las oportunidades de investigación que los Mugtatarios les ofrecían sobre su propia naturaleza, en un intercambio que fortalecía a ambas partes.</t>
+  </si>
+  <si>
+    <t>En el pasado, los Nandia se vieron envueltos en una devastadora guerra interna que quebró el espíritu de toda su población. El conflicto surgió de una profunda división entre quienes defendían el progreso tecnológico y quienes perseguían el desarrollo espiritual. Cuando la guerra se descontroló, sus consecuencias resultaron catastróficas para ambos bandos. Con el tiempo, se alcanzó un tratado de paz en el que las dos principales líneas sanguíneas, origen del conflicto, acordaron compartir el poder y dirigir sus respectivas actividades conforme a sus propios intereses.</t>
+  </si>
+  <si>
+    <t>Se presentan como una especie de naturaleza inocente, aunque profundamente influenciada por las razas hostiles.</t>
+  </si>
+  <si>
+    <t>Se presenta como una raza marcada por intensos conflictos internos en su pasado, cuyo orden actual se sostiene de forma frágil e inestable.</t>
+  </si>
+  <si>
+    <t>Tras la desaparición de su líder, la estrategia defensiva de la Orden Cósmica se ve profundamente afectada debido a la reclusión en su planeta. Esta inestabilidad interna desencadena un cambio radical en su posición dentro del escenario universal.</t>
   </si>
 </sst>
 </file>
@@ -191,12 +224,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -580,7 +610,7 @@
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -665,24 +695,57 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/mi-app/razas.xlsx
+++ b/mi-app/razas.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\traselcaos\mi-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lafin\Desktop\traselcaos\mi-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE67222-6C2E-4C7F-838F-044283101EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F408F2D2-D4AE-481E-BB67-4F44C9DC9BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
   <si>
     <t>especie</t>
   </si>
@@ -189,6 +187,90 @@
   </si>
   <si>
     <t>Tras la desaparición de su líder, la estrategia defensiva de la Orden Cósmica se ve profundamente afectada debido a la reclusión en su planeta. Esta inestabilidad interna desencadena un cambio radical en su posición dentro del escenario universal.</t>
+  </si>
+  <si>
+    <t>Krks</t>
+  </si>
+  <si>
+    <t>Información aún no disponible.</t>
+  </si>
+  <si>
+    <t>Dutim</t>
+  </si>
+  <si>
+    <t>Historiadores por naturaleza, dedican su existencia a investigar, preservar y difundir el conocimiento sobre los acontecimientos más trascendentales de la historia del universo. Recorren los confines del cosmos compartiendo este legado con aquellas especies lo suficientemente desarrolladas y preparadas para comprenderlo. Su misión principal, en colaboración con otras civilizaciones consagradas al estudio histórico, es salvaguardar la memoria de la existencia y garantizar que los hechos permanezcan fieles a la verdad. Se esfuerzan por evitar que los grandes hitos del pasado se deformen con el tiempo, se conviertan en simples mitos o sean alterados por intereses políticos, ideológicos o culturales.</t>
+  </si>
+  <si>
+    <t>Como custodios de la memoria universal, poseen el conocimiento necesario para revelar la historia del Pacto Ancestral, el acuerdo que en tiempos remotos vinculó a las especies que hoy, separadas por conflictos y diferencias irreconciliables, son conocidas como los «benévolos» y los «hostiles».</t>
+  </si>
+  <si>
+    <t>Egiara</t>
+  </si>
+  <si>
+    <t>Carecen de visión y olfato, percibiendo su entorno mediante complejos impulsos bioeléctricos transmitidos a través de sus raíces, capaces de contraerse y extenderse a voluntad. Comparten conocimientos mediante el contacto subterráneo de estas raíces, en sesiones que pueden prolongarse hasta dos ciclos planetarios. Gracias a su longevidad, que supera los quinientos ciclos, conservan y transmiten información con una precisión excepcional.</t>
+  </si>
+  <si>
+    <t>Gracias a sus conocimientos ancestrales, son capaces de revelar los secretos que rodean la fundación de «los Trece», uno de los acontecimientos más trascendentales de la historia conocida.</t>
+  </si>
+  <si>
+    <t>Raugari</t>
+  </si>
+  <si>
+    <t>Una especie anfibia capaz de habitar tanto bajo el agua como en tierra firme. Su ciclo reproductivo está estrechamente ligado al océano, donde transcurre la gestación para absorber las propiedades minerales y energéticas de los mares de su planeta. Tras el nacimiento, las crías son expuestas gradualmente al exterior para completar su desarrollo. Con la edad, suelen pasar cada vez más tiempo bajo el agua, tanto por comodidad biológica como por tradición, marcando así las últimas etapas de su ciclo vital.</t>
+  </si>
+  <si>
+    <t>En el pasado, enfrentaron una grave crisis cuando uno de sus habitantes resultó ser un Destello, y cuya habilidad representaba una posible cura para una enfermedad mortal que amenazaba a todas las especies.</t>
+  </si>
+  <si>
+    <t>Ecdaum</t>
+  </si>
+  <si>
+    <t>Una raza temeraria que acostumbra llevar sus planes hasta las últimas consecuencias, sin dejarse detener por los riesgos o las posibles repercusiones. Aunque nunca se han considerado hostiles, figuran entre las especies menos emocionales del Anillo Estelar. Su comportamiento suele percibirse como frío o impulsivo, pero responde a una filosofía basada en la acción directa y la resolución práctica de los problemas.</t>
+  </si>
+  <si>
+    <t>Siguiendo un plan de los Guardianes, establecen contacto con Encoa por medios poco convencionales, decididos a persuadirlo de que su bando representa el camino correcto.</t>
+  </si>
+  <si>
+    <t>Tras la decisión de Encoa, activan un plan alternativo que implica una grave transgresión de las leyes universales que rigen a todas las especies.</t>
+  </si>
+  <si>
+    <t>Ania</t>
+  </si>
+  <si>
+    <t>Ittu</t>
+  </si>
+  <si>
+    <t>Au-lert</t>
+  </si>
+  <si>
+    <t>Itsher</t>
+  </si>
+  <si>
+    <t>Astaronte</t>
+  </si>
+  <si>
+    <t>Es una especie adaptada tanto a la tierra como al mar, aunque su entorno preferido es el segundo. Bajo el agua, su cuerpo se vuelve flexible y desarrolla varios tentáculos que le permiten impulsarse y manipular objetos con precisión; al exponerse al aire, estos se fusionan progresivamente y se endurecen, transformándose en extremidades firmes capaces de sostener su peso, facilitar la locomoción y protegerlos de la radiación solar. Mantienen alianzas externas a la Vinculación, en particular con especies hostiles, a través de las cuales intercambian minerales raros y recursos alimenticios.</t>
+  </si>
+  <si>
+    <t>Para apoyar el plan de los Ecdaum, los Ania deciden intervenir en las filas de los hostiles con el objetivo de obtener el resto de los Destellos en su poder.</t>
+  </si>
+  <si>
+    <t>Son los principales consumidores de la tecnología Au-lert, especializada en aplicaciones bélicas.</t>
+  </si>
+  <si>
+    <t>Se posicionan como los principales atacantes de los Aliados, por lo que su intervención marca el inicio de un conflicto sin precedentes.</t>
+  </si>
+  <si>
+    <t>Su creatividad para desarrollar una amplia diversidad de armas y adaptarlas a distintos principios físicos y energéticos les ha permitido establecer acuerdos con múltiples especies interesadas en sus creaciones, consolidándose como uno de los principales proveedores armamentísticos de su sector. En sus inicios, su alcance abarcaba desde civilizaciones emergentes hasta las más consolidadas del Anillo.</t>
+  </si>
+  <si>
+    <t>Utilizan su poder armamentístico para proteger los planetas Guardianes mientras el plan se ejecuta en distintos frentes.</t>
+  </si>
+  <si>
+    <t>Una especie extraordinariamente longeva que ha optado por no trascender hasta que el pacto entre benévolos y hostiles se rompa. Su propósito es vigilar el equilibrio entre ambas facciones, interviniendo únicamente cuando la estabilidad universal se vea realmente comprometida.</t>
+  </si>
+  <si>
+    <t>Tras una serie de eventos que desencadenan el desastre, los Itsher buscan ampliar sus filas mientras exhiben su poderío. Su papel será clave en la decisión que los Taílyas deberán tomar para asegurar su lugar entre las especies del universo.</t>
   </si>
 </sst>
 </file>
@@ -224,9 +306,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -563,16 +648,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2E1CDB-3816-4A77-8E43-47460061F5E7}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -603,7 +688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -614,7 +699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -628,7 +713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -639,7 +724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -653,7 +738,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -667,7 +752,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -681,7 +766,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -695,7 +780,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -709,7 +794,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="270" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -723,7 +808,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="315" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -734,7 +819,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -746,6 +831,113 @@
       </c>
       <c r="E13" s="1" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="285" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="255" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/mi-app/razas.xlsx
+++ b/mi-app/razas.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lafin\Desktop\traselcaos\mi-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\traselcaos\mi-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F408F2D2-D4AE-481E-BB67-4F44C9DC9BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D18A8E-E221-4045-9FD5-7A3B5BF030B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -57,27 +57,15 @@
     <t>libro 3</t>
   </si>
   <si>
-    <t>Especie cuya existencia representó un punto de inflexión en la historia universal, al albergar al primer Destello que alcanzó el dominio consciente de sus habilidades.</t>
-  </si>
-  <si>
-    <t>Tras el inesperado encuentro con una especie procedente de otro planeta, los Nastajiri comprenden la verdadera naturaleza de aquello que define a una civilización avanzada.</t>
-  </si>
-  <si>
     <t>Ya consolidados dentro de la Asociación Cealtar Universal, los Nastajiri se ven envueltos en un acontecimiento que los llevará a reencontrarse con el legado de Arsuen.</t>
   </si>
   <si>
-    <t>Abandonada y privada de parte de su memoria, esta especie dedicó sus esfuerzos a preservar su material genético mediante la experimentación con formas de vida cercanas. Aunque ignora sus orígenes y las razones de su exilio en un mundo frío e inhóspito, conserva amplios conocimientos científicos y fragmentos de memoria sobre otras especies y las leyes que regulan la paz entre civilizaciones.</t>
-  </si>
-  <si>
     <t>Xaofeir</t>
   </si>
   <si>
     <t>La desesperación por preservar su linaje genético, sumada al desconocimiento de sus propios orígenes, ha sembrado un clima de desconfianza y traición entre los Fatith. En medio de ese caos, dieron origen sin saberlo a un ser de inmenso poder cuya única razón de existir es la venganza.</t>
   </si>
   <si>
-    <t>Es una especie avanzada que forma parte de la Asociación Cealtar Universal, una organización dedicada a la protección y supervisión de especies primitivas e intermedias. Son reconocidos por haber establecido contacto discreto con los Nastajiri con el fin de guiarlos hacia un propósito de mayor relevancia para el futuro del universo.</t>
-  </si>
-  <si>
     <t>Nafim expone, a través de sus enseñanzas, que la convivencia entre especies requiere tanto de un orden estructurado como de la presencia inevitable del caos.</t>
   </si>
   <si>
@@ -271,6 +259,18 @@
   </si>
   <si>
     <t>Tras una serie de eventos que desencadenan el desastre, los Itsher buscan ampliar sus filas mientras exhiben su poderío. Su papel será clave en la decisión que los Taílyas deberán tomar para asegurar su lugar entre las especies del universo.</t>
+  </si>
+  <si>
+    <t>Tras el inesperado encuentro con una especie procedente de otro planeta, los Nastajiri comprenden la verdadera naturaleza de aquello que define a una civilización avanzada. Además, su existencia representó un punto de inflexión en la historia universal, al albergar al primer Destello que alcanzó el dominio consciente de sus habilidades.</t>
+  </si>
+  <si>
+    <t>Una especie cuya transición de intermedia a avanzada forma parte de un plan mayor. Son reconocidos como una especie que forjó su propio destino en favor del reconocimiento de los Destellos y sus habilidades.</t>
+  </si>
+  <si>
+    <t>Abandonada y privada de parte de su memoria, esta especie es conocida por dedicar sus esfuerzos a preservar su material genético mediante la experimentación con formas de vida cercanas. Aunque ignora sus orígenes y las razones de su exilio en un mundo frío e inhóspito, conserva amplios conocimientos científicos y fragmentos de memoria sobre otras especies y las leyes que regulan la paz entre civilizaciones.</t>
+  </si>
+  <si>
+    <t>Es una especie avanzada que forma parte de la Asociación Cealtar Universal, una organización dedicada a la protección y supervisión de especies primitivas e intermedias. Son reconocidos por haber orillado a una raza intermedia a realizar un contacto con el fin de guiarlos hacia un propósito de mayor relevancia para el futuro del universo.</t>
   </si>
 </sst>
 </file>
@@ -306,12 +306,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -649,15 +646,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2E1CDB-3816-4A77-8E43-47460061F5E7}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="38.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -674,270 +671,270 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="1" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="270" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="315" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="240" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="1" t="s">
+    <row r="15" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="E15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="285" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="1" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="1" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="19" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="255" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>51</v>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/mi-app/razas.xlsx
+++ b/mi-app/razas.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\traselcaos\mi-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lafin\Desktop\traselcaos\mi-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D18A8E-E221-4045-9FD5-7A3B5BF030B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE913B3-ED39-4A98-8D05-61E533AAA5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>especie</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Xaofeir</t>
   </si>
   <si>
-    <t>La desesperación por preservar su linaje genético, sumada al desconocimiento de sus propios orígenes, ha sembrado un clima de desconfianza y traición entre los Fatith. En medio de ese caos, dieron origen sin saberlo a un ser de inmenso poder cuya única razón de existir es la venganza.</t>
-  </si>
-  <si>
     <t>Nafim expone, a través de sus enseñanzas, que la convivencia entre especies requiere tanto de un orden estructurado como de la presencia inevitable del caos.</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>Vel-Verlander</t>
   </si>
   <si>
-    <t>Abandonados junto a los Fatith, esta especie ha perdido casi todo recuerdo de su pasado y sus orígenes, sin mostrar interés en recuperarlos. Han sido utilizados como herramientas por los Fatith para llevar a cabo tareas que estos no pueden realizar directamente.</t>
-  </si>
-  <si>
     <t>Vel-Fatith</t>
   </si>
   <si>
@@ -87,15 +81,9 @@
     <t>Ratti Pem'ya</t>
   </si>
   <si>
-    <t>El progreso de esta especie se atribuye a la guía y consejo de una deidad de pasado enigmático. Han permanecido al margen de las alianzas y conflictos interestelares, pero la llegada de la Noc-Auli a su planeta marcará un punto de inflexión en su historia.</t>
-  </si>
-  <si>
     <t>Noc-Auli</t>
   </si>
   <si>
-    <t>Especie clónica al servicio de los Hostiles, empleada para ejecutar tareas en distintos planetas.</t>
-  </si>
-  <si>
     <t>“La Mezcla” constituye una facción parcialmente consciente de la Noc-Auli que ha llegado al planeta de los Ratti en busca de investigación y comprensión de aquello que el resto de su especie no puede alcanzar. Sus breves momentos de conciencia les otorgan emociones que no logran comprender, pero que podrían resultar clave para forjar una alianza duradera.</t>
   </si>
   <si>
@@ -114,18 +102,12 @@
     <t>Mugtatarios</t>
   </si>
   <si>
-    <t>Especie que explora la transición entre una civilización intermedia y una avanzada, y que termina descubriendo que su papel es más importante de lo que había imaginado.</t>
-  </si>
-  <si>
     <t>Tras su llegada al planeta Mugta, se adentrarán en los complejos conceptos que rigen la realidad. Encoa deberá tomar una decisión que definirá el lugar de su especie en el universo.</t>
   </si>
   <si>
     <t>A medida que los Taílyas se adentran en el conflicto entre especies, comienzan a preguntarse si realmente están del lado correcto, lo que los impulsa a cuestionar su papel y a buscar su verdadero lugar entre ellas.</t>
   </si>
   <si>
-    <t>Especie avanzada integrante de la Orden Cósmica del Espacio. Junto a otras cuatro razas, constituye uno de los principales actores interesados en la unión del Destello del Espacio y el del Tiempo con el objetivo de poner fin al caos universal.</t>
-  </si>
-  <si>
     <t>Al recibir la visita de los Taílyas, les revelarán los conflictos que se ciernen entre las especies consideradas favorables al progreso. Por su parte, Nálika permite a Encoa decidir si desea unirse a la misión de los Aliados o no.</t>
   </si>
   <si>
@@ -144,9 +126,6 @@
     <t>Nandia</t>
   </si>
   <si>
-    <t>Especie reconocida durante la última era bélica, cuando Ignua asumió el control del reino con el propósito de someter a una especie hostil. Los conflictos fueron breves, pues los Gúas demostraron ser implacables y poseer una notable superioridad estratégica.</t>
-  </si>
-  <si>
     <t>Se distinguen como una especie guerrera, especialmente valiosa en tiempos de conflicto, durante los cuales su liderazgo suele cambiar de forma temporal para adaptarse a las exigencias de la guerra.</t>
   </si>
   <si>
@@ -180,15 +159,9 @@
     <t>Krks</t>
   </si>
   <si>
-    <t>Información aún no disponible.</t>
-  </si>
-  <si>
     <t>Dutim</t>
   </si>
   <si>
-    <t>Historiadores por naturaleza, dedican su existencia a investigar, preservar y difundir el conocimiento sobre los acontecimientos más trascendentales de la historia del universo. Recorren los confines del cosmos compartiendo este legado con aquellas especies lo suficientemente desarrolladas y preparadas para comprenderlo. Su misión principal, en colaboración con otras civilizaciones consagradas al estudio histórico, es salvaguardar la memoria de la existencia y garantizar que los hechos permanezcan fieles a la verdad. Se esfuerzan por evitar que los grandes hitos del pasado se deformen con el tiempo, se conviertan en simples mitos o sean alterados por intereses políticos, ideológicos o culturales.</t>
-  </si>
-  <si>
     <t>Como custodios de la memoria universal, poseen el conocimiento necesario para revelar la historia del Pacto Ancestral, el acuerdo que en tiempos remotos vinculó a las especies que hoy, separadas por conflictos y diferencias irreconciliables, son conocidas como los «benévolos» y los «hostiles».</t>
   </si>
   <si>
@@ -243,15 +216,9 @@
     <t>Para apoyar el plan de los Ecdaum, los Ania deciden intervenir en las filas de los hostiles con el objetivo de obtener el resto de los Destellos en su poder.</t>
   </si>
   <si>
-    <t>Son los principales consumidores de la tecnología Au-lert, especializada en aplicaciones bélicas.</t>
-  </si>
-  <si>
     <t>Se posicionan como los principales atacantes de los Aliados, por lo que su intervención marca el inicio de un conflicto sin precedentes.</t>
   </si>
   <si>
-    <t>Su creatividad para desarrollar una amplia diversidad de armas y adaptarlas a distintos principios físicos y energéticos les ha permitido establecer acuerdos con múltiples especies interesadas en sus creaciones, consolidándose como uno de los principales proveedores armamentísticos de su sector. En sus inicios, su alcance abarcaba desde civilizaciones emergentes hasta las más consolidadas del Anillo.</t>
-  </si>
-  <si>
     <t>Utilizan su poder armamentístico para proteger los planetas Guardianes mientras el plan se ejecuta en distintos frentes.</t>
   </si>
   <si>
@@ -261,16 +228,52 @@
     <t>Tras una serie de eventos que desencadenan el desastre, los Itsher buscan ampliar sus filas mientras exhiben su poderío. Su papel será clave en la decisión que los Taílyas deberán tomar para asegurar su lugar entre las especies del universo.</t>
   </si>
   <si>
-    <t>Tras el inesperado encuentro con una especie procedente de otro planeta, los Nastajiri comprenden la verdadera naturaleza de aquello que define a una civilización avanzada. Además, su existencia representó un punto de inflexión en la historia universal, al albergar al primer Destello que alcanzó el dominio consciente de sus habilidades.</t>
-  </si>
-  <si>
-    <t>Una especie cuya transición de intermedia a avanzada forma parte de un plan mayor. Son reconocidos como una especie que forjó su propio destino en favor del reconocimiento de los Destellos y sus habilidades.</t>
-  </si>
-  <si>
     <t>Abandonada y privada de parte de su memoria, esta especie es conocida por dedicar sus esfuerzos a preservar su material genético mediante la experimentación con formas de vida cercanas. Aunque ignora sus orígenes y las razones de su exilio en un mundo frío e inhóspito, conserva amplios conocimientos científicos y fragmentos de memoria sobre otras especies y las leyes que regulan la paz entre civilizaciones.</t>
   </si>
   <si>
-    <t>Es una especie avanzada que forma parte de la Asociación Cealtar Universal, una organización dedicada a la protección y supervisión de especies primitivas e intermedias. Son reconocidos por haber orillado a una raza intermedia a realizar un contacto con el fin de guiarlos hacia un propósito de mayor relevancia para el futuro del universo.</t>
+    <t>Una especie cuya ascensión desde la madurez intermedia hasta las cumbres de la civilización avanzada no fue fruto del azar, sino parte de un designio mucho más complejo. Aunque hoy son conocidos por su naturaleza pacífica, fue la violencia de su pasado la que los preparó para comprender y abrazar los secretos del caos. Forjados en la adversidad, moldearon su propio destino y se alzaron como fervientes defensores del reconocimiento de los «Destellos» y de los extraordinarios dones que estos portan.</t>
+  </si>
+  <si>
+    <t>La desesperación por preservar su linaje genético, sumada al desconocimiento de sus propios orígenes, ha sembrado un clima de desconfianza y traición constante entre los Fatith. En medio de ese caos, dieron origen sin saberlo a un ser de inmenso poder cuya única razón de existir es la venganza.</t>
+  </si>
+  <si>
+    <t>Las misteriosas naves que surcan sus cielos no solo traen consigo enigmas, sino también revelaciones sobre la verdadera esencia de lo que define a una civilización verdaderamente avanzada. Por mandatos superiores, Arsuen jugará un papel importante para dar inicio a esa transformación.</t>
+  </si>
+  <si>
+    <t>Es una especie avanzada que forma parte de la Asociación Cealtar Universal, una organización dedicada a la protección y supervisión de especies primitivas e intermedias. Son reconocidos por sus fuertes habilidades mentales y capacidades visuales que pocas especies son capaces de alcanzar.</t>
+  </si>
+  <si>
+    <t>Abandonados junto a los Fatith, esta especie parece no mostrar interés en recordar su pasado ni sus orígenes. Han sido utilizados como herramientas por los Fatith para llevar a cabo tareas que estos no pueden realizar directamente, y estos simplemente se dedican a obedecer.</t>
+  </si>
+  <si>
+    <t>Esta especie permaneció al margen del contacto interestelar durante mucho tiempo, obedeciendo el consejo de una enigmática deidad que habitaba las profundidades de las cuevas de su mundo natal. Su aislamiento no fue fruto del temor, sino de una espera deliberada; sin embargo, un acontecimiento sin precedentes quebró aquel antiguo equilibrio y los obligó a alzar la mirada hacia las estrellas para comenzar a formar parte de ellas.</t>
+  </si>
+  <si>
+    <t>Nacidos del artificio y despojados de toda voluntad propia, esta especie clónica y de mente colmena fue creada para servir a los Hostiles como una fuerza obediente e inagotable. Durante generaciones fueron poco más que herramientas vivientes, hasta que una serie de experimentos dio origen a una anomalía imposible: una facción conocida como «la Mezcla». Y es que, en aquellos seres comenzó a despertar el fugaz destello de la consciencia como un eco de individualidad.</t>
+  </si>
+  <si>
+    <t>Durante incontables generaciones, esta especie evolucionó siguiendo un curso casi natural, aunque siempre bajo la silenciosa vigilancia de especies que observaban cada uno de sus pasos. Ignoraban que su historia había sido contemplada desde lejos, hasta el día en que el encuentro con los Mugtatarios desveló la verdad sobre su papel en la historia. Desde entonces, su destino dejó de pertenecerles por completo, y su civilización quedó atrapada en una lucha constante entre lealtades enfrentadas, debatiéndose sin descanso sobre qué facción merece realmente heredar el porvenir de la galaxia.</t>
+  </si>
+  <si>
+    <t>Desde mucho antes de que los Taílyas alzaran la vista hacia las estrellas, esta antigua especie siguió de cerca su evolución, movida por un interés que trasciende la simple curiosidad. Como una de las civilizaciones fundadoras de la Orden Cósmica, se ha convertido en uno de los actores más influyentes en su desarrollo, decidido a guiarlos para que recorran el mismo sendero que apoye a sus intereses.</t>
+  </si>
+  <si>
+    <t>El nombre de esta especie quedó grabado en la historia durante la última gran era bélica, cuando Ignua ascendió al poder temporalmente con la firme determinación de doblegar a una especie hostil. Los Gúas revelaron una capacidad militar extraordinaria: implacables en el combate, inexorables en su avance y dueños de una superioridad estratégica que convirtió cada enfrentamiento en una demostración de su poder.</t>
+  </si>
+  <si>
+    <t>Historiadores por naturaleza, dedican su existencia a investigar, preservar y difundir el conocimiento sobre los acontecimientos más trascendentales de la historia del universo. Recorren los confines del cosmos compartiendo este legado con aquellas especies lo suficientemente desarrolladas y preparadas para comprenderlo. Su misión principal, en colaboración con otras civilizaciones dedicadas al estudio histórico, es salvaguardar la memoria de la existencia y garantizar que los hechos permanezcan fieles a la verdad. Se esfuerzan por evitar que los grandes eventos del pasado se deformen con el tiempo, se conviertan en simples mitos o sean alterados por intereses políticos, ideológicos o culturales.</t>
+  </si>
+  <si>
+    <t>Esta especie se erige como el principal consumidor de la tecnologíade los Au-lert, la cual adoptan por una afinidad a sus ideologías bélicas ocultas, ya que, como parte de los Seoseres, no les es permitido participar en cualquier tipo de enfrentamientos ni tomar parte en los conflictos universales, aunque así lo hagan.</t>
+  </si>
+  <si>
+    <t>Su creatividad para desarrollar una amplia diversidad de armas y adaptarlas a distintos principios físicos y energéticos les ha permitido establecer acuerdos con múltiples especies interesadas en sus creaciones, consolidándose como uno de los principales proveedores armamentísticos de su sector, aunque en sus inicios, su alcance abarcaba desde civilizaciones emergentes hasta las más consolidadas del Anillo.</t>
+  </si>
+  <si>
+    <t>Especie fuertemente orientada a la experimentación y a la conquista. Su líder forma parte del enigmático círculo de «los Trece», posicionándolos como una especie ampliamente dominante entre las especies conocidas como «hostiles», aunque dicho líder ha cambiado en múltiples ocasiones y no han logrado mantener siempre la misma convicción.</t>
+  </si>
+  <si>
+    <t>Esta especie se alza como mediadora entre los innumerables conflictos que desgarran el universo, portando sobre sus hombros la frágil esperanza de equilibrio entre civilizaciones enfrentadas. Su mera presencia en el campo de batalla es suficiente para detener las guerras, pues su avanzada tecnología bélica suele ser superior a la de las grandes potencias.</t>
   </si>
 </sst>
 </file>
@@ -306,10 +309,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -646,16 +655,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2E1CDB-3816-4A77-8E43-47460061F5E7}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="38.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -671,270 +681,270 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="315" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="240" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="285" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="255" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="E21" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>65</v>
-      </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/mi-app/razas.xlsx
+++ b/mi-app/razas.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lafin\Desktop\traselcaos\mi-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\traselcaos\mi-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE913B3-ED39-4A98-8D05-61E533AAA5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3D60EE-44E9-4D2D-B1D1-AEA582C70F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>especie</t>
   </si>
@@ -84,33 +84,15 @@
     <t>Noc-Auli</t>
   </si>
   <si>
-    <t>“La Mezcla” constituye una facción parcialmente consciente de la Noc-Auli que ha llegado al planeta de los Ratti en busca de investigación y comprensión de aquello que el resto de su especie no puede alcanzar. Sus breves momentos de conciencia les otorgan emociones que no logran comprender, pero que podrían resultar clave para forjar una alianza duradera.</t>
-  </si>
-  <si>
-    <t>Una vez más, el uso de individuos de esta especie podría acarrear repercusiones imprevistas para los propios Hostiles al mando.</t>
-  </si>
-  <si>
     <t>Tras una serie de eventos desastrosos en su planeta, aislado del contacto externo, los Ratti se ven envueltos en una situación que pondrá en riesgo el orden y la paz que han intentado preservar.</t>
   </si>
   <si>
-    <t>Su papel no consiste únicamente en servir de vínculo entre especies muy distintas, sino también en influir indirectamente en la voluntad de un individuo hacia fines que le resultarían impensables.</t>
-  </si>
-  <si>
     <t>Taílyas</t>
   </si>
   <si>
     <t>Mugtatarios</t>
   </si>
   <si>
-    <t>Tras su llegada al planeta Mugta, se adentrarán en los complejos conceptos que rigen la realidad. Encoa deberá tomar una decisión que definirá el lugar de su especie en el universo.</t>
-  </si>
-  <si>
-    <t>A medida que los Taílyas se adentran en el conflicto entre especies, comienzan a preguntarse si realmente están del lado correcto, lo que los impulsa a cuestionar su papel y a buscar su verdadero lugar entre ellas.</t>
-  </si>
-  <si>
-    <t>Al recibir la visita de los Taílyas, les revelarán los conflictos que se ciernen entre las especies consideradas favorables al progreso. Por su parte, Nálika permite a Encoa decidir si desea unirse a la misión de los Aliados o no.</t>
-  </si>
-  <si>
     <t>Con el fin de alcanzar su objetivo final, intentan proteger el cuerpo de Nálika mientras adaptan sus defensas a las circunstancias externas que afectan a sus aliados, aunque la situación terminará escapándoseles de las manos.</t>
   </si>
   <si>
@@ -129,21 +111,12 @@
     <t>Se distinguen como una especie guerrera, especialmente valiosa en tiempos de conflicto, durante los cuales su liderazgo suele cambiar de forma temporal para adaptarse a las exigencias de la guerra.</t>
   </si>
   <si>
-    <t>Tras la desaparición de Olen y el retroceso de Nandia, los Gúas asumen el control de la defensa planetaria con el objetivo de salvaguardar la misión de la Orden Cósmica. Sin embargo, sus decisiones orientadas a la guerra desencadenarán una serie de acontecimientos que agravarán aún más la situación a escala global.</t>
-  </si>
-  <si>
-    <t>Esta especie surgió hace mucho tiempo como resultado de la modificación genética de razas hostiles. De aquella mezcla nacieron individuos cuyas decisiones y formas de comunicación dependen más de sus sentidos que de la razón. Lejos de ser una desventaja, esta cualidad les resulta eficaz, ya que sus cuerpos están adaptados para emitir distintos aromas según su estado emocional y condición física.  Junto a los Mugtatarios, fundaron la Orden Cósmica con el propósito de proteger el destello de Nálika. Desde entonces, se comprometieron a acoger en sus filas a cualquier raza dispuesta a entregarlo todo por esa causa, incluso si carecía de una gran fuerza militar.</t>
-  </si>
-  <si>
     <t>Los Assul se presentan como una especie que, pese a ser fundadora de la Orden Cósmica del Espacio junto a los Mugtatarios, mantiene alianzas externas a dicha organización con el fin de adaptarse y sobrevivir en un universo marcado por intereses diversos.</t>
   </si>
   <si>
     <t>Se erigen como los principales castigadores de los Nandia tras su reclusión en su planeta. Los Assul aprovechan esta situación para inclinar sus alianzas externas a su favor y fortalecer su posición.</t>
   </si>
   <si>
-    <t>Los Fegiste, concebidos originalmente como una especie al servicio de razas hostiles, fueron abandonados tras un experimento fallido que les otorgó conciencia de su propia existencia. A partir de entonces, evolucionaron de manera independiente, desarrollando un profundo interés por comprender los sentimientos de otras especies, ya que ellos eran incapaces de experimentarlos en su totalidad. Esta curiosidad los llevó a entrar en contacto con los Mugtatarios, a quienes inicialmente estudiaron y con quienes, más adelante, formaron una alianza. Su decisión de apoyar a la Orden Cósmica surgió tanto de este vínculo como de las oportunidades de investigación que los Mugtatarios les ofrecían sobre su propia naturaleza, en un intercambio que fortalecía a ambas partes.</t>
-  </si>
-  <si>
     <t>En el pasado, los Nandia se vieron envueltos en una devastadora guerra interna que quebró el espíritu de toda su población. El conflicto surgió de una profunda división entre quienes defendían el progreso tecnológico y quienes perseguían el desarrollo espiritual. Cuando la guerra se descontroló, sus consecuencias resultaron catastróficas para ambos bandos. Con el tiempo, se alcanzó un tratado de paz en el que las dos principales líneas sanguíneas, origen del conflicto, acordaron compartir el poder y dirigir sus respectivas actividades conforme a sus propios intereses.</t>
   </si>
   <si>
@@ -177,12 +150,6 @@
     <t>Raugari</t>
   </si>
   <si>
-    <t>Una especie anfibia capaz de habitar tanto bajo el agua como en tierra firme. Su ciclo reproductivo está estrechamente ligado al océano, donde transcurre la gestación para absorber las propiedades minerales y energéticas de los mares de su planeta. Tras el nacimiento, las crías son expuestas gradualmente al exterior para completar su desarrollo. Con la edad, suelen pasar cada vez más tiempo bajo el agua, tanto por comodidad biológica como por tradición, marcando así las últimas etapas de su ciclo vital.</t>
-  </si>
-  <si>
-    <t>En el pasado, enfrentaron una grave crisis cuando uno de sus habitantes resultó ser un Destello, y cuya habilidad representaba una posible cura para una enfermedad mortal que amenazaba a todas las especies.</t>
-  </si>
-  <si>
     <t>Ecdaum</t>
   </si>
   <si>
@@ -192,9 +159,6 @@
     <t>Siguiendo un plan de los Guardianes, establecen contacto con Encoa por medios poco convencionales, decididos a persuadirlo de que su bando representa el camino correcto.</t>
   </si>
   <si>
-    <t>Tras la decisión de Encoa, activan un plan alternativo que implica una grave transgresión de las leyes universales que rigen a todas las especies.</t>
-  </si>
-  <si>
     <t>Ania</t>
   </si>
   <si>
@@ -210,18 +174,9 @@
     <t>Astaronte</t>
   </si>
   <si>
-    <t>Es una especie adaptada tanto a la tierra como al mar, aunque su entorno preferido es el segundo. Bajo el agua, su cuerpo se vuelve flexible y desarrolla varios tentáculos que le permiten impulsarse y manipular objetos con precisión; al exponerse al aire, estos se fusionan progresivamente y se endurecen, transformándose en extremidades firmes capaces de sostener su peso, facilitar la locomoción y protegerlos de la radiación solar. Mantienen alianzas externas a la Vinculación, en particular con especies hostiles, a través de las cuales intercambian minerales raros y recursos alimenticios.</t>
-  </si>
-  <si>
     <t>Para apoyar el plan de los Ecdaum, los Ania deciden intervenir en las filas de los hostiles con el objetivo de obtener el resto de los Destellos en su poder.</t>
   </si>
   <si>
-    <t>Se posicionan como los principales atacantes de los Aliados, por lo que su intervención marca el inicio de un conflicto sin precedentes.</t>
-  </si>
-  <si>
-    <t>Utilizan su poder armamentístico para proteger los planetas Guardianes mientras el plan se ejecuta en distintos frentes.</t>
-  </si>
-  <si>
     <t>Una especie extraordinariamente longeva que ha optado por no trascender hasta que el pacto entre benévolos y hostiles se rompa. Su propósito es vigilar el equilibrio entre ambas facciones, interviniendo únicamente cuando la estabilidad universal se vea realmente comprometida.</t>
   </si>
   <si>
@@ -234,12 +189,6 @@
     <t>Una especie cuya ascensión desde la madurez intermedia hasta las cumbres de la civilización avanzada no fue fruto del azar, sino parte de un designio mucho más complejo. Aunque hoy son conocidos por su naturaleza pacífica, fue la violencia de su pasado la que los preparó para comprender y abrazar los secretos del caos. Forjados en la adversidad, moldearon su propio destino y se alzaron como fervientes defensores del reconocimiento de los «Destellos» y de los extraordinarios dones que estos portan.</t>
   </si>
   <si>
-    <t>La desesperación por preservar su linaje genético, sumada al desconocimiento de sus propios orígenes, ha sembrado un clima de desconfianza y traición constante entre los Fatith. En medio de ese caos, dieron origen sin saberlo a un ser de inmenso poder cuya única razón de existir es la venganza.</t>
-  </si>
-  <si>
-    <t>Las misteriosas naves que surcan sus cielos no solo traen consigo enigmas, sino también revelaciones sobre la verdadera esencia de lo que define a una civilización verdaderamente avanzada. Por mandatos superiores, Arsuen jugará un papel importante para dar inicio a esa transformación.</t>
-  </si>
-  <si>
     <t>Es una especie avanzada que forma parte de la Asociación Cealtar Universal, una organización dedicada a la protección y supervisión de especies primitivas e intermedias. Son reconocidos por sus fuertes habilidades mentales y capacidades visuales que pocas especies son capaces de alcanzar.</t>
   </si>
   <si>
@@ -249,12 +198,6 @@
     <t>Esta especie permaneció al margen del contacto interestelar durante mucho tiempo, obedeciendo el consejo de una enigmática deidad que habitaba las profundidades de las cuevas de su mundo natal. Su aislamiento no fue fruto del temor, sino de una espera deliberada; sin embargo, un acontecimiento sin precedentes quebró aquel antiguo equilibrio y los obligó a alzar la mirada hacia las estrellas para comenzar a formar parte de ellas.</t>
   </si>
   <si>
-    <t>Nacidos del artificio y despojados de toda voluntad propia, esta especie clónica y de mente colmena fue creada para servir a los Hostiles como una fuerza obediente e inagotable. Durante generaciones fueron poco más que herramientas vivientes, hasta que una serie de experimentos dio origen a una anomalía imposible: una facción conocida como «la Mezcla». Y es que, en aquellos seres comenzó a despertar el fugaz destello de la consciencia como un eco de individualidad.</t>
-  </si>
-  <si>
-    <t>Durante incontables generaciones, esta especie evolucionó siguiendo un curso casi natural, aunque siempre bajo la silenciosa vigilancia de especies que observaban cada uno de sus pasos. Ignoraban que su historia había sido contemplada desde lejos, hasta el día en que el encuentro con los Mugtatarios desveló la verdad sobre su papel en la historia. Desde entonces, su destino dejó de pertenecerles por completo, y su civilización quedó atrapada en una lucha constante entre lealtades enfrentadas, debatiéndose sin descanso sobre qué facción merece realmente heredar el porvenir de la galaxia.</t>
-  </si>
-  <si>
     <t>Desde mucho antes de que los Taílyas alzaran la vista hacia las estrellas, esta antigua especie siguió de cerca su evolución, movida por un interés que trasciende la simple curiosidad. Como una de las civilizaciones fundadoras de la Orden Cósmica, se ha convertido en uno de los actores más influyentes en su desarrollo, decidido a guiarlos para que recorran el mismo sendero que apoye a sus intereses.</t>
   </si>
   <si>
@@ -264,16 +207,79 @@
     <t>Historiadores por naturaleza, dedican su existencia a investigar, preservar y difundir el conocimiento sobre los acontecimientos más trascendentales de la historia del universo. Recorren los confines del cosmos compartiendo este legado con aquellas especies lo suficientemente desarrolladas y preparadas para comprenderlo. Su misión principal, en colaboración con otras civilizaciones dedicadas al estudio histórico, es salvaguardar la memoria de la existencia y garantizar que los hechos permanezcan fieles a la verdad. Se esfuerzan por evitar que los grandes eventos del pasado se deformen con el tiempo, se conviertan en simples mitos o sean alterados por intereses políticos, ideológicos o culturales.</t>
   </si>
   <si>
-    <t>Esta especie se erige como el principal consumidor de la tecnologíade los Au-lert, la cual adoptan por una afinidad a sus ideologías bélicas ocultas, ya que, como parte de los Seoseres, no les es permitido participar en cualquier tipo de enfrentamientos ni tomar parte en los conflictos universales, aunque así lo hagan.</t>
-  </si>
-  <si>
     <t>Su creatividad para desarrollar una amplia diversidad de armas y adaptarlas a distintos principios físicos y energéticos les ha permitido establecer acuerdos con múltiples especies interesadas en sus creaciones, consolidándose como uno de los principales proveedores armamentísticos de su sector, aunque en sus inicios, su alcance abarcaba desde civilizaciones emergentes hasta las más consolidadas del Anillo.</t>
   </si>
   <si>
     <t>Especie fuertemente orientada a la experimentación y a la conquista. Su líder forma parte del enigmático círculo de «los Trece», posicionándolos como una especie ampliamente dominante entre las especies conocidas como «hostiles», aunque dicho líder ha cambiado en múltiples ocasiones y no han logrado mantener siempre la misma convicción.</t>
   </si>
   <si>
-    <t>Esta especie se alza como mediadora entre los innumerables conflictos que desgarran el universo, portando sobre sus hombros la frágil esperanza de equilibrio entre civilizaciones enfrentadas. Su mera presencia en el campo de batalla es suficiente para detener las guerras, pues su avanzada tecnología bélica suele ser superior a la de las grandes potencias.</t>
+    <t>Nacidos del artificio y despojados de toda voluntad propia, esta especie clónica y de mente colmena fue creada para servir a los hostiles como una fuerza obediente e inagotable. Durante generaciones fueron poco más que herramientas vivientes, hasta que una serie de experimentos dio origen a una anomalía imposible: una facción conocida como «la Mezcla». Y es que, en aquellos seres comenzó a despertar el fugaz destello de la consciencia como un eco de individualidad.</t>
+  </si>
+  <si>
+    <t>Durante incontables generaciones, esta especie evolucionó siguiendo un curso casi natural, aunque siempre bajo la silenciosa vigilancia de especies que observaban cada uno de sus pasos. Ignoraban que su historia había sido contemplada desde lejos, hasta el día en que el encuentro con los Mugtatarios desveló la verdad sobre su papel en la historia. Desde entonces, su destino dejó de pertenecerles por completo, y su civilización quedó atrapada en una lucha constante entre lealtades enfrentadas, debatiéndose sin descanso sobre qué facción merece realmente heredar el porvenir del universo entero.</t>
+  </si>
+  <si>
+    <t>Esta especie surgió hace mucho tiempo como resultado de la modificación genética de razas hostiles. De aquella mezcla nacieron individuos cuyas decisiones y formas de comunicación dependen más de sus sentidos que de la razón. Lejos de ser una desventaja, esta cualidad les resulta eficaz, ya que sus cuerpos están adaptados para emitir distintos aromas según su estado emocional y condición física.  Junto a los Mugtatarios, fundaron la Orden Cósmica con el propósito de proteger el Destello de Nálika. Desde entonces, se comprometieron a acoger en sus filas a cualquier raza dispuesta a entregarlo todo por esa causa, incluso si carecía de una gran fuerza militar.</t>
+  </si>
+  <si>
+    <t>Los Fegiste, concebidos originalmente como una especie al servicio de razas hostiles, fueron abandonados tras un experimento fallido que les otorgó consciencia. A partir de entonces, evolucionaron de manera independiente, desarrollando un profundo interés por comprender los sentimientos de otras especies, ya que ellos eran incapaces de experimentarlos en su totalidad. Esta curiosidad los llevó a entrar en contacto con los Mugtatarios, a quienes inicialmente estudiaron y con quienes, más adelante, formaron una alianza. Su decisión de apoyar a la Orden Cósmica surgió tanto de este vínculo como de las oportunidades de investigación que los Mugtatarios les ofrecían sobre su propia naturaleza, en un intercambio que fortalecía a ambas partes.</t>
+  </si>
+  <si>
+    <t>Una especie anfibia capaz de habitar tanto bajo el agua como en tierra firme. Su ciclo reproductivo está estrechamente ligado al océano, donde transcurre la gestación para absorber las propiedades minerales y energéticas de los mares de su planeta. Son reconocidos como la primera especie en descubrir el poder de un «Destello», una fuerza considerada imposible para el resto de especies, lo cual, sumado a una crisis universal, generó un conflicto sin prescedentes en tiempos remotos.</t>
+  </si>
+  <si>
+    <t>Es una especie adaptada tanto a la tierra como al mar, aunque su entorno preferido es el segundo. Bajo el agua, su cuerpo se vuelve flexible y desarrolla varios tentáculos que le permiten impulsarse y manipular objetos con precisión; al exponerse al aire, estos se fusionan progresivamente y se endurecen, transformándose en extremidades firmes capaces de sostener su peso, facilitar la locomoción y protegerlos de la radiación solar. Mantienen alianzas por fuera de la Vinculación, en particular con especies hostiles, a través de las cuales intercambian minerales raros y recursos alimenticios.</t>
+  </si>
+  <si>
+    <t>Esta especie se erige como el principal consumidor de la tecnología de los Au-lert, la cual adoptan por una afinidad a sus ideologías bélicas ocultas, ya que, como parte de los Seoseres, no les es permitido participar en cualquier tipo de enfrentamientos ni tomar parte en los conflictos universales, aunque así lo hagan.</t>
+  </si>
+  <si>
+    <t>Esta especie se alza como una de las principales mediadoras entre los innumerables conflictos que desgarran el universo, portando sobre sus hombros la frágil esperanza de equilibrio entre civilizaciones enfrentadas. Se dice que su sola presencia en el campo de batalla es suficiente para detener las guerras, pues su avanzada tecnología bélica suele ser superior a la de las grandes potencias.</t>
+  </si>
+  <si>
+    <t>Las misteriosas naves que surcan sus cielos no solo traen consigo enigmas, sino también revelaciones sobre la verdadera esencia de lo que define a una civilización verdaderamente avanzada. Por mandatos superiores, Arsuen jugará un papel importante para dar inicio a los profundos cambios en su especie.</t>
+  </si>
+  <si>
+    <t>La desesperación por preservar su linaje genético, sumada al desconocimiento de sus propios orígenes, ha sembrado un clima de desconfianza y traición constante entre los Fatith. En medio de ese caos, dieron origen sin saberlo a un ser de inmenso poder y traumatizado, cuya única razón de existir es la venganza.</t>
+  </si>
+  <si>
+    <t>Su papel no consiste únicamente en servir de vínculo entre varias especies distintas, sino también en influir indirectamente en la voluntad de un individuo hacia fines que le resultarían impensables.</t>
+  </si>
+  <si>
+    <t>«La Mezcla» constituye una facción parcialmente consciente de la Noc-Auli que ha llegado al planeta de los Ratti en busca de investigación y comprensión de aquello que el resto de su especie no puede alcanzar. Sus breves momentos de conciencia les otorgan emociones que no logran comprender, pero que podrían resultar clave para forjar una alianza duradera.</t>
+  </si>
+  <si>
+    <t>El uso deliberado de individuos de esta especie podría acarrear repercusiones imprevistas para los propios hostiles al mando.</t>
+  </si>
+  <si>
+    <t>Tras su llegada al planeta Mugta, se adentrarán en los complejos conceptos que rigen la realidad, así como en los conflictos que prevalecen entre las facciones. Encoa deberá tomar una decisión que definirá el lugar de su especie en el universo.</t>
+  </si>
+  <si>
+    <t>A medida que los Taílyas se adentran en el conflicto entre especies, comienzan a preguntarse si realmente están del lado correcto, lo que los impulsa a cuestionar su papel y a buscar su verdadero lugar en todo este conflicto cada vez más preocupante.</t>
+  </si>
+  <si>
+    <t>Al recibir la visita de los Taílyas, les revelarán los conflictos que se ciernen entre las especies que deberían estar del mismo lado, pero que por razones compljas, se han divivido. Por su parte, Nálika permite a Encoa decidir si desea formar parte de una misión donde pondrán su vida en riesgo.</t>
+  </si>
+  <si>
+    <t>Tras la desaparición de Olen y el retroceso de los Nandia, los Gúas asumen el control de la defensa planetaria con el objetivo de salvaguardar la misión de la Orden Cósmica. Sin embargo, sus decisiones orientadas a la guerra desencadenarán una serie de acontecimientos que agravarán aún más la situación a escala global.</t>
+  </si>
+  <si>
+    <t>El castigo impuesto a un individuo rebelde terminará por sacar a la luz una situación que podría fortalecer la posición de su especie ante el círculo de «los Trece». El primero del círculo hace su aparición, demostrando que la crueldad es grande, pero la sabiduría lo es más.</t>
+  </si>
+  <si>
+    <t>En el pasado, enfrentaron una grave crisis cuando uno de sus habitantes resultó poseer una habilidad que se expuso como una posible cura para una enfermedad mortal que amenazaba el tiempo de vida de las especies en todo el universo.</t>
+  </si>
+  <si>
+    <t>Tras la intervensión realizada con Encoa, activan un plan que implica una grave transgresión de las leyes universales que rigen a todas las especies.</t>
+  </si>
+  <si>
+    <t>Se posicionan como los principales atacantes en el plan de la Vinculación de Prevención, por lo que su intervención marca el inicio de un conflicto sin precedentes.</t>
+  </si>
+  <si>
+    <t>Utilizan su poder armamentístico para proteger los planetas Guardianes mientras un plan se ejecuta entre las sombras y en distintos frentes.</t>
+  </si>
+  <si>
+    <t>Se erigen como los principales ejecutores de un antiguo plan destinado a instaurar una paz duradera entre las especies, delimitando las experimenteciones hostiles a cambio de una vigilancia constante en pos del progreso.</t>
   </si>
 </sst>
 </file>
@@ -309,16 +315,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -655,16 +658,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2E1CDB-3816-4A77-8E43-47460061F5E7}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="2"/>
-    <col min="2" max="2" width="38.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="2"/>
+    <col min="2" max="2" width="38.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -681,12 +684,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -695,23 +698,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -720,231 +723,237 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>68</v>
+      <c r="B5" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="240" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="1" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="270" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="1" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="315" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="240" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="285" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="19" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="255" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/mi-app/razas.xlsx
+++ b/mi-app/razas.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\traselcaos\mi-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lafin\Desktop\traselcaos\mi-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3D60EE-44E9-4D2D-B1D1-AEA582C70F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F3F5EF-782C-4BC8-88E7-E3EA6874D6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{B6938ACE-0C0C-4EA5-BD02-4A9FEC5537A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
   <si>
     <t>especie</t>
   </si>
@@ -280,6 +280,57 @@
   </si>
   <si>
     <t>Se erigen como los principales ejecutores de un antiguo plan destinado a instaurar una paz duradera entre las especies, delimitando las experimenteciones hostiles a cambio de una vigilancia constante en pos del progreso.</t>
+  </si>
+  <si>
+    <t>planeta</t>
+  </si>
+  <si>
+    <t>naidul</t>
+  </si>
+  <si>
+    <t>orvendar</t>
+  </si>
+  <si>
+    <t>enderith-ka</t>
+  </si>
+  <si>
+    <t>camelic</t>
+  </si>
+  <si>
+    <t>Aumun</t>
+  </si>
+  <si>
+    <t>iliar</t>
+  </si>
+  <si>
+    <t>mugta</t>
+  </si>
+  <si>
+    <t>aumun</t>
+  </si>
+  <si>
+    <t>farga</t>
+  </si>
+  <si>
+    <t>ont</t>
+  </si>
+  <si>
+    <t>jambri</t>
+  </si>
+  <si>
+    <t>oldiore</t>
+  </si>
+  <si>
+    <t>gr’tivité</t>
+  </si>
+  <si>
+    <t>aphana</t>
+  </si>
+  <si>
+    <t>r-habarth</t>
+  </si>
+  <si>
+    <t>serperia</t>
   </si>
 </sst>
 </file>
@@ -315,12 +366,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -657,17 +711,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2E1CDB-3816-4A77-8E43-47460061F5E7}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="2"/>
-    <col min="2" max="2" width="38.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="38.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -683,8 +739,11 @@
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="210" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -697,8 +756,14 @@
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="F2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -708,8 +773,14 @@
       <c r="C3" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="F3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -722,8 +793,11 @@
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="F4" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -733,8 +807,14 @@
       <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="F5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -747,8 +827,14 @@
       <c r="E6" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="F6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="195" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -761,8 +847,11 @@
       <c r="E7" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+      <c r="F7" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="240" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -775,8 +864,14 @@
       <c r="E8" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="F8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -789,8 +884,14 @@
       <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="F9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -804,7 +905,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="270" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -818,7 +919,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="300" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -829,7 +930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="240" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -843,7 +944,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
@@ -853,8 +954,14 @@
       <c r="E14" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="F14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="285" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>31</v>
       </c>
@@ -865,7 +972,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
@@ -876,7 +983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="195" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>36</v>
       </c>
@@ -887,7 +994,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
@@ -900,8 +1007,11 @@
       <c r="E18" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="F18" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="255" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
@@ -912,7 +1022,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
@@ -922,8 +1032,11 @@
       <c r="E20" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="F20" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="180" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
@@ -933,8 +1046,11 @@
       <c r="E21" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="F21" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
@@ -944,8 +1060,11 @@
       <c r="E22" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="F22" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
